--- a/data/trans_orig/IP1014-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1014-Provincia-trans_orig.xlsx
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105175</t>
+          <t>105531</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>207120</t>
+          <t>207179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75779</t>
+          <t>75218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149957</t>
+          <t>150554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41315</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83834</t>
+          <t>83570</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131589</t>
+          <t>132263</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260286</t>
+          <t>261040</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4054</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>154323</t>
+          <t>154368</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160582</t>
+          <t>160538</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317006</t>
+          <t>317908</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>678079</t>
+          <t>677995</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>715780</t>
+          <t>714541</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>721379</t>
+          <t>721349</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1395022</t>
+          <t>1395565</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1402338</t>
+          <t>1402370</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57593</t>
+          <t>57796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111410</t>
+          <t>110827</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3620</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>107864</t>
+          <t>107360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212252</t>
+          <t>212242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>6484</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72609</t>
+          <t>72395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77517</t>
+          <t>78219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154191</t>
+          <t>153511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159552</t>
+          <t>159547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55359</t>
+          <t>55444</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112121</t>
+          <t>111378</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142625</t>
+          <t>142408</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>280893</t>
+          <t>281118</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>3371</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>168229</t>
+          <t>167949</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331524</t>
+          <t>332652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>702001</t>
+          <t>700603</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>739056</t>
+          <t>738888</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>746133</t>
+          <t>746185</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1443713</t>
+          <t>1443362</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1452308</t>
+          <t>1451880</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>42318</t>
+          <t>42558</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85373</t>
+          <t>85358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53881</t>
+          <t>54357</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>109089</t>
+          <t>108448</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10157,47 +10157,47 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5357</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>739487</t>
+          <t>739598</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>744227</t>
+          <t>744225</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1443872</t>
+          <t>1443342</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1448600</t>
+          <t>1448598</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/IP1014-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1014-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -840,42 +840,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>642</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3226</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3140</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108115</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>104919</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108115</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>105531</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>207179</t>
+          <t>207091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3418</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78438</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75745</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>78438</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>75218</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150554</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>705</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3535</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4035</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3125</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44138</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>41322</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44138</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>41308</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83570</t>
+          <t>82660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,107 +2780,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>679</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>679</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3392</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3237</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>134976</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>132246</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>134976</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>132263</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>261040</t>
+          <t>261166</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3128,102 +3128,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3634</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3536</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3598</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3520</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4675</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4054</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3236,74 +3236,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>163358</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>160424</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>157262</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>154368</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>154306</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,59%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>163358</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>160538</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>492</t>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317908</t>
+          <t>317287</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>7549</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>3026</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3590</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8159</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>719301</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>715151</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>721353</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>680379</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>677995</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>677431</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>719301</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>714541</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>721349</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2098</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1395565</t>
+          <t>1395462</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1402370</t>
+          <t>1401802</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4045,107 +4045,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>572</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>572</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2871</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2898</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4158,72 +4158,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60189</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>58030</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60189</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>57796</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110827</t>
+          <t>110854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4388,107 +4388,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>654</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3799</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3605</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3630</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -4501,72 +4501,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110505</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>107925</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110505</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>107360</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212242</t>
+          <t>212267</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4844,47 +4844,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5074,107 +5074,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4008</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5366</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4568</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4015</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,87%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2132</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5920</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6484</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -5187,107 +5187,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81441</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78226</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76422</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>72395</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>73193</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,13%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81441</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>78219</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>157863</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>154075</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>159995</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>96,3%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>157863</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>153511</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>159547</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,67%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5530,47 +5530,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5760,107 +5760,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1376</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4801</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4817</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1376</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4852</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -5873,72 +5873,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>58869</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>55917</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>92,82%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>58869</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>55444</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111378</t>
+          <t>111413</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6103,107 +6103,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>624</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>624</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3331</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3093</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3339</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -6216,72 +6216,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145115</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>142175</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145115</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>142408</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>281118</t>
+          <t>281364</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6446,107 +6446,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3391</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3366</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3878</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3371</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -6559,72 +6559,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170642</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>167924</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>98,02%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170642</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>167949</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>332652</t>
+          <t>332145</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6789,72 +6789,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>9563</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>6325</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5560</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>4691</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>9254</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -6902,74 +6902,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>743451</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>738579</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>746107</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>705589</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>700603</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>701368</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>743451</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>738888</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>746185</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2075</t>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1443362</t>
+          <t>1444532</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1451880</t>
+          <t>1452399</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7481,47 +7481,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7824,47 +7824,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8167,47 +8167,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8510,47 +8510,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8740,107 +8740,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1280</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3792</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3999</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4430</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -8853,72 +8853,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>45070</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>41911</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,42%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>45070</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>42558</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,24%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85358</t>
+          <t>85789</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9083,107 +9083,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>715</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>715</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3382</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4255</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,86%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3564</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -9196,72 +9196,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57024</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>53501</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>92,66%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57024</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>54357</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>108448</t>
+          <t>107757</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9539,47 +9539,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9882,47 +9882,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,84 +10112,84 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5246</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
           <t>617</t>
@@ -10197,7 +10197,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -10225,72 +10225,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>742849</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>739143</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>744250</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>742849</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>739598</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>744225</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1443342</t>
+          <t>1443163</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
